--- a/USA_WB_timeseries.xlsx
+++ b/USA_WB_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Control of Corruption</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Foreign direct investment, net outflows (BoP, current US$)</t>
   </si>
   <si>
+    <t>GDP (current US$)</t>
+  </si>
+  <si>
     <t>GDP growth (annual %)</t>
   </si>
   <si>
@@ -41,6 +44,9 @@
   </si>
   <si>
     <t>Gini index</t>
+  </si>
+  <si>
+    <t>Government consumption (% of GDP)</t>
   </si>
   <si>
     <t>Government expenditure (% of GDP)</t>
@@ -437,12 +443,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:X36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -507,8 +513,14 @@
       <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -528,46 +540,52 @@
         <v>59940000000</v>
       </c>
       <c r="H2">
+        <v>5963144000000</v>
+      </c>
+      <c r="I2">
         <v>1.88596558335223</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>23888.6000088133</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>38.3</v>
       </c>
-      <c r="K2">
+      <c r="L2">
+        <v>15.9007731491978</v>
+      </c>
+      <c r="M2">
         <v>21.5589293164814</v>
       </c>
-      <c r="L2">
+      <c r="N2">
         <v>18.2058323595741</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>10.5603352862181</v>
       </c>
-      <c r="N2">
+      <c r="P2">
         <v>5.39795643990325</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>15.2723652175266</v>
       </c>
-      <c r="P2">
+      <c r="R2">
         <v>-3.66652222384702</v>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>10.4652847558268</v>
       </c>
-      <c r="S2">
+      <c r="U2">
         <v>173093564607.845</v>
       </c>
-      <c r="T2">
+      <c r="V2">
         <v>2.73557589265657</v>
       </c>
-      <c r="U2">
+      <c r="W2">
         <v>19.8150673537315</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:24">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -587,49 +605,55 @@
         <v>49270000000</v>
       </c>
       <c r="H3">
+        <v>6158129000000</v>
+      </c>
+      <c r="I3">
         <v>-0.108312881913292</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>24342.2589048189</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>38</v>
       </c>
-      <c r="K3">
+      <c r="L3">
+        <v>16.3175860720034</v>
+      </c>
+      <c r="M3">
         <v>22.8843858256298</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>18.1313187820521</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>10.1255430017786</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>4.23496396453849</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>15.5366329607947</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>-4.37032092052635</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>10.3203424286825</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <v>159272850288.003</v>
       </c>
-      <c r="T3">
+      <c r="V3">
         <v>2.60169338107099</v>
       </c>
-      <c r="U3">
+      <c r="W3">
         <v>19.7864481240974</v>
       </c>
-      <c r="V3">
+      <c r="X3">
         <v>6.8</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:24">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -649,49 +673,55 @@
         <v>58770000000</v>
       </c>
       <c r="H4">
+        <v>6520327000000</v>
+      </c>
+      <c r="I4">
         <v>3.52249717698845</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>25418.9907763319</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>38.4</v>
       </c>
-      <c r="K4">
+      <c r="L4">
+        <v>16.0786874646011</v>
+      </c>
+      <c r="M4">
         <v>21.8183842620163</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>17.6483480046323</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>10.2416795967442</v>
       </c>
-      <c r="N4">
+      <c r="P4">
         <v>3.02881967814969</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>15.2225104208403</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>-4.4235511501187</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>9.984161837282089</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>147525874735.105</v>
       </c>
-      <c r="T4">
+      <c r="V4">
         <v>2.31231476555185</v>
       </c>
-      <c r="U4">
+      <c r="W4">
         <v>19.9505945023923</v>
       </c>
-      <c r="V4">
+      <c r="X4">
         <v>7.5</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:24">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -711,49 +741,55 @@
         <v>82800000000</v>
       </c>
       <c r="H5">
+        <v>6858559000000</v>
+      </c>
+      <c r="I5">
         <v>2.7517958662618</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>26387.2937338171</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>40.4</v>
       </c>
-      <c r="K5">
+      <c r="L5">
+        <v>15.6452689260237</v>
+      </c>
+      <c r="M5">
         <v>21.4174726790278</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>18.0456273686645</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>10.4974383102923</v>
       </c>
-      <c r="N5">
+      <c r="P5">
         <v>2.95165696638559</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>14.363516300981</v>
       </c>
-      <c r="P5">
+      <c r="R5">
         <v>-3.69654908560238</v>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>10.3049343163775</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>164620171357.293</v>
       </c>
-      <c r="T5">
+      <c r="V5">
         <v>2.39765174502404</v>
       </c>
-      <c r="U5">
+      <c r="W5">
         <v>20.0446187019752</v>
       </c>
-      <c r="V5">
+      <c r="X5">
         <v>6.9</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:24">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -773,49 +809,55 @@
         <v>89990000000</v>
       </c>
       <c r="H6">
+        <v>7287236000000</v>
+      </c>
+      <c r="I6">
         <v>4.02902272603258</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>27694.853416234</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>40</v>
       </c>
-      <c r="K6">
+      <c r="L6">
+        <v>15.2060534337024</v>
+      </c>
+      <c r="M6">
         <v>20.7314542852736</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>18.2572651688514</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>11.162311746182</v>
       </c>
-      <c r="N6">
+      <c r="P6">
         <v>2.60744159215453</v>
       </c>
-      <c r="O6">
+      <c r="Q6">
         <v>14.1863312924044</v>
       </c>
-      <c r="P6">
+      <c r="R6">
         <v>-2.79104450576323</v>
       </c>
-      <c r="R6">
+      <c r="T6">
         <v>10.6235066354376</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <v>163590579764.938</v>
       </c>
-      <c r="T6">
+      <c r="V6">
         <v>2.06391324712794</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <v>21.0554591617453</v>
       </c>
-      <c r="V6">
+      <c r="X6">
         <v>6.119</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:24">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -835,49 +877,55 @@
         <v>110060000000</v>
       </c>
       <c r="H7">
+        <v>7639749000000</v>
+      </c>
+      <c r="I7">
         <v>2.68443073360764</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>28690.8757013347</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>39.9</v>
       </c>
-      <c r="K7">
+      <c r="L7">
+        <v>14.9447710913016</v>
+      </c>
+      <c r="M7">
         <v>20.5330044220039</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>18.7804599339586</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>11.8141577687958</v>
       </c>
-      <c r="N7">
+      <c r="P7">
         <v>2.80541968853662</v>
       </c>
-      <c r="O7">
+      <c r="Q7">
         <v>14.9279325798288</v>
       </c>
-      <c r="P7">
+      <c r="R7">
         <v>-1.97872992947805</v>
       </c>
-      <c r="R7">
+      <c r="T7">
         <v>10.980989035111</v>
       </c>
-      <c r="S7">
+      <c r="U7">
         <v>175995426883.436</v>
       </c>
-      <c r="T7">
+      <c r="V7">
         <v>1.95523553618241</v>
       </c>
-      <c r="U7">
+      <c r="W7">
         <v>22.4533816490568</v>
       </c>
-      <c r="V7">
+      <c r="X7">
         <v>5.65</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:24">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -900,52 +948,58 @@
         <v>103020000000</v>
       </c>
       <c r="H8">
+        <v>8073122000000</v>
+      </c>
+      <c r="I8">
         <v>3.77277269138068</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>29967.7127181749</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>40.3</v>
       </c>
-      <c r="K8">
+      <c r="L8">
+        <v>14.5283200229106</v>
+      </c>
+      <c r="M8">
         <v>20.0053956821165</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>18.9521476326011</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>11.9404364259576</v>
       </c>
-      <c r="N8">
+      <c r="P8">
         <v>2.93120419993441</v>
       </c>
-      <c r="O8">
+      <c r="Q8">
         <v>15.6229489926071</v>
       </c>
-      <c r="P8">
+      <c r="R8">
         <v>-1.38087842596705</v>
       </c>
-      <c r="Q8">
+      <c r="S8">
         <v>0.935005784034729</v>
       </c>
-      <c r="R8">
+      <c r="T8">
         <v>11.373914577285</v>
       </c>
-      <c r="S8">
+      <c r="U8">
         <v>160660160546.204</v>
       </c>
-      <c r="T8">
+      <c r="V8">
         <v>1.66275864603054</v>
       </c>
-      <c r="U8">
+      <c r="W8">
         <v>22.6870719902412</v>
       </c>
-      <c r="V8">
+      <c r="X8">
         <v>5.451</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:24">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -965,49 +1019,55 @@
         <v>121380000000</v>
       </c>
       <c r="H9">
+        <v>8577552000000</v>
+      </c>
+      <c r="I9">
         <v>4.44712793805328</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>31459.1299691554</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>40.5</v>
       </c>
-      <c r="K9">
+      <c r="L9">
+        <v>14.2293395598185</v>
+      </c>
+      <c r="M9">
         <v>19.3896813449805</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>19.4159126053681</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>12.3085700908604</v>
       </c>
-      <c r="N9">
+      <c r="P9">
         <v>2.33768993730735</v>
       </c>
-      <c r="O9">
+      <c r="Q9">
         <v>15.2985882296352</v>
       </c>
-      <c r="P9">
+      <c r="R9">
         <v>-0.231068258169697</v>
       </c>
-      <c r="R9">
+      <c r="T9">
         <v>11.8281999339672</v>
       </c>
-      <c r="S9">
+      <c r="U9">
         <v>134836033327.141</v>
       </c>
-      <c r="T9">
+      <c r="V9">
         <v>1.2572687990174</v>
       </c>
-      <c r="U9">
+      <c r="W9">
         <v>23.4283278026178</v>
       </c>
-      <c r="V9">
+      <c r="X9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:24">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -1030,52 +1090,58 @@
         <v>174760000000</v>
       </c>
       <c r="H10">
+        <v>9062817000000</v>
+      </c>
+      <c r="I10">
         <v>4.48313335029331</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>32853.6725949234</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>40</v>
       </c>
-      <c r="K10">
+      <c r="L10">
+        <v>13.9869093682461</v>
+      </c>
+      <c r="M10">
         <v>18.7213313476373</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>19.8287133018354</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>12.3106314515674</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>1.55227909874364</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>14.92326189971</v>
       </c>
-      <c r="P10">
+      <c r="R10">
         <v>0.800634063338143</v>
       </c>
-      <c r="Q10">
+      <c r="S10">
         <v>0.879612982273102</v>
       </c>
-      <c r="R10">
+      <c r="T10">
         <v>12.3298307799882</v>
       </c>
-      <c r="S10">
+      <c r="U10">
         <v>146006089507.341</v>
       </c>
-      <c r="T10">
+      <c r="V10">
         <v>1.29127119690475</v>
       </c>
-      <c r="U10">
+      <c r="W10">
         <v>22.8258939797637</v>
       </c>
-      <c r="V10">
+      <c r="X10">
         <v>4.511</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:24">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -1095,49 +1161,55 @@
         <v>247485000000</v>
       </c>
       <c r="H11">
+        <v>9631172000000</v>
+      </c>
+      <c r="I11">
         <v>4.78842504949371</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>34515.3813073394</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>40</v>
       </c>
-      <c r="K11">
+      <c r="L11">
+        <v>14.0318125353799</v>
+      </c>
+      <c r="M11">
         <v>18.1044425330583</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>19.7821199745991</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>13.004232506698</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <v>2.18802719697358</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>13.8248636496585</v>
       </c>
-      <c r="P11">
+      <c r="R11">
         <v>1.28675928537046</v>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>12.2599824818828</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>136450101867.481</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>1.07377331452326</v>
       </c>
-      <c r="U11">
+      <c r="W11">
         <v>23.3135697296238</v>
       </c>
-      <c r="V11">
+      <c r="X11">
         <v>4.219</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:24">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -1160,52 +1232,58 @@
         <v>186370000000</v>
       </c>
       <c r="H12">
+        <v>10250952000000</v>
+      </c>
+      <c r="I12">
         <v>4.07758576006954</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>36329.9702595751</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>40.1</v>
       </c>
-      <c r="K12">
+      <c r="L12">
+        <v>14.0239462637226</v>
+      </c>
+      <c r="M12">
         <v>17.9265301408103</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>20.576137708966</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>14.4102128270623</v>
       </c>
-      <c r="N12">
+      <c r="P12">
         <v>3.37685727149929</v>
       </c>
-      <c r="O12">
+      <c r="Q12">
         <v>12.8621492784223</v>
       </c>
-      <c r="P12">
+      <c r="R12">
         <v>2.23364620183569</v>
       </c>
-      <c r="Q12">
+      <c r="S12">
         <v>1.08280909061432</v>
       </c>
-      <c r="R12">
+      <c r="T12">
         <v>12.9707952978416</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>128399516602.723</v>
       </c>
-      <c r="T12">
+      <c r="V12">
         <v>0.854272096906953</v>
       </c>
-      <c r="U12">
+      <c r="W12">
         <v>25.1029855568536</v>
       </c>
-      <c r="V12">
+      <c r="X12">
         <v>3.992</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:24">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -1225,49 +1303,55 @@
         <v>146041000000</v>
       </c>
       <c r="H13">
+        <v>10581929000000</v>
+      </c>
+      <c r="I13">
         <v>0.95553834188668</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>37133.6203973517</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>40.6</v>
       </c>
-      <c r="K13">
+      <c r="L13">
+        <v>14.535639012509</v>
+      </c>
+      <c r="M13">
         <v>19.5097642405274</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>19.5089146789777</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>13.2637348067635</v>
       </c>
-      <c r="N13">
+      <c r="P13">
         <v>2.82617111885407</v>
       </c>
-      <c r="O13">
+      <c r="Q13">
         <v>12.5250870739557</v>
       </c>
-      <c r="P13">
+      <c r="R13">
         <v>0.0139813827894706</v>
       </c>
-      <c r="R13">
+      <c r="T13">
         <v>11.8577047719749</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>130076677027.985</v>
       </c>
-      <c r="T13">
+      <c r="V13">
         <v>0.938134144021969</v>
       </c>
-      <c r="U13">
+      <c r="W13">
         <v>22.9671830154975</v>
       </c>
-      <c r="V13">
+      <c r="X13">
         <v>4.731</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:24">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -1290,52 +1374,58 @@
         <v>178985000000</v>
       </c>
       <c r="H14">
+        <v>10929108000000</v>
+      </c>
+      <c r="I14">
         <v>1.7004473278454</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>37997.7424300242</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>40.4</v>
       </c>
-      <c r="K14">
+      <c r="L14">
+        <v>15.059033180018</v>
+      </c>
+      <c r="M14">
         <v>20.0840187506611</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>17.3842220243409</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>13.1549985598093</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>1.58603162650601</v>
       </c>
-      <c r="O14">
+      <c r="Q14">
         <v>10.372518210786</v>
       </c>
-      <c r="P14">
+      <c r="R14">
         <v>-2.84500802810257</v>
       </c>
-      <c r="Q14">
+      <c r="S14">
         <v>0.285476922988892</v>
       </c>
-      <c r="R14">
+      <c r="T14">
         <v>9.86801667620084</v>
       </c>
-      <c r="S14">
+      <c r="U14">
         <v>157762914914.241</v>
       </c>
-      <c r="T14">
+      <c r="V14">
         <v>1.11647810305723</v>
       </c>
-      <c r="U14">
+      <c r="W14">
         <v>22.2863842136065</v>
       </c>
-      <c r="V14">
+      <c r="X14">
         <v>5.783</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:24">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -1358,52 +1448,58 @@
         <v>195218000000</v>
       </c>
       <c r="H15">
+        <v>11456450000000</v>
+      </c>
+      <c r="I15">
         <v>2.79560596521233</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>39490.3023903176</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>40.8</v>
       </c>
-      <c r="K15">
+      <c r="L15">
+        <v>15.243622588149</v>
+      </c>
+      <c r="M15">
         <v>20.6606182543458</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>16.7774293083809</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>13.5916448812678</v>
       </c>
-      <c r="N15">
+      <c r="P15">
         <v>2.27009497336115</v>
       </c>
-      <c r="O15">
+      <c r="Q15">
         <v>8.98132611038214</v>
       </c>
-      <c r="P15">
+      <c r="R15">
         <v>-4.07842394459017</v>
       </c>
-      <c r="Q15">
+      <c r="S15">
         <v>0.0804403498768806</v>
       </c>
-      <c r="R15">
+      <c r="T15">
         <v>9.3906925792894</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>184024332193.35</v>
       </c>
-      <c r="T15">
+      <c r="V15">
         <v>1.19878399570069</v>
       </c>
-      <c r="U15">
+      <c r="W15">
         <v>22.6272972866813</v>
       </c>
-      <c r="V15">
+      <c r="X15">
         <v>5.989</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:24">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -1426,52 +1522,58 @@
         <v>374004000000</v>
       </c>
       <c r="H16">
+        <v>12217196000000</v>
+      </c>
+      <c r="I16">
         <v>3.84777169424153</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>41724.6411982614</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>40.5</v>
       </c>
-      <c r="K16">
+      <c r="L16">
+        <v>15.1583063740649</v>
+      </c>
+      <c r="M16">
         <v>20.4485309067645</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>16.8434344509166</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>14.8193087841105</v>
       </c>
-      <c r="N16">
+      <c r="P16">
         <v>2.67723669309172</v>
       </c>
-      <c r="O16">
+      <c r="Q16">
         <v>8.83871670947485</v>
       </c>
-      <c r="P16">
+      <c r="R16">
         <v>-3.82684864841327</v>
       </c>
-      <c r="Q16">
+      <c r="S16">
         <v>-0.233039826154709</v>
       </c>
-      <c r="R16">
+      <c r="T16">
         <v>9.53747079117008</v>
       </c>
-      <c r="S16">
+      <c r="U16">
         <v>190464790633.305</v>
       </c>
-      <c r="T16">
+      <c r="V16">
         <v>1.05559111218244</v>
       </c>
-      <c r="U16">
+      <c r="W16">
         <v>24.4480566571904</v>
       </c>
-      <c r="V16">
+      <c r="X16">
         <v>5.529</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:24">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -1494,52 +1596,58 @@
         <v>52591000000</v>
       </c>
       <c r="H17">
+        <v>13039197000000</v>
+      </c>
+      <c r="I17">
         <v>3.48354993544559</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>44123.3996470026</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>41.3</v>
       </c>
-      <c r="K17">
+      <c r="L17">
+        <v>15.0471459247069</v>
+      </c>
+      <c r="M17">
         <v>20.7451064662954</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>17.928590234506</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>15.6565009333013</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <v>3.3927468454955</v>
       </c>
-      <c r="O17">
+      <c r="Q17">
         <v>9.51690747854534</v>
       </c>
-      <c r="P17">
+      <c r="R17">
         <v>-3.03664635176537</v>
       </c>
-      <c r="Q17">
+      <c r="S17">
         <v>-0.0605432577431202</v>
       </c>
-      <c r="R17">
+      <c r="T17">
         <v>10.6817329318669</v>
       </c>
-      <c r="S17">
+      <c r="U17">
         <v>188259141662.468</v>
       </c>
-      <c r="T17">
+      <c r="V17">
         <v>0.903588941772187</v>
       </c>
-      <c r="U17">
+      <c r="W17">
         <v>25.6385573436769</v>
       </c>
-      <c r="V17">
+      <c r="X17">
         <v>5.084</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:24">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -1562,52 +1670,58 @@
         <v>283801000000</v>
       </c>
       <c r="H18">
+        <v>13815583000000</v>
+      </c>
+      <c r="I18">
         <v>2.78453963817891</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>46301.9876485519</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>41.7</v>
       </c>
-      <c r="K18">
+      <c r="L18">
+        <v>15.0044627143132</v>
+      </c>
+      <c r="M18">
         <v>20.5951410085264</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>18.6287129540606</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>16.3338962966673</v>
       </c>
-      <c r="N18">
+      <c r="P18">
         <v>3.22594410070404</v>
       </c>
-      <c r="O18">
+      <c r="Q18">
         <v>9.86093114816415</v>
       </c>
-      <c r="P18">
+      <c r="R18">
         <v>-2.10572293619459</v>
       </c>
-      <c r="Q18">
+      <c r="S18">
         <v>0.49083548784256</v>
       </c>
-      <c r="R18">
+      <c r="T18">
         <v>11.3104788990808</v>
       </c>
-      <c r="S18">
+      <c r="U18">
         <v>221088725058.691</v>
       </c>
-      <c r="T18">
+      <c r="V18">
         <v>0.920734980795974</v>
       </c>
-      <c r="U18">
+      <c r="W18">
         <v>26.9752858058903</v>
       </c>
-      <c r="V18">
+      <c r="X18">
         <v>4.623</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:24">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -1630,52 +1744,58 @@
         <v>523890000000</v>
       </c>
       <c r="H19">
+        <v>14474228000000</v>
+      </c>
+      <c r="I19">
         <v>2.00385829909158</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>48050.227412195</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>41.1</v>
       </c>
-      <c r="K19">
+      <c r="L19">
+        <v>15.1892936880641</v>
+      </c>
+      <c r="M19">
         <v>20.8646436963685</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>18.6567829386134</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>16.5482262680953</v>
       </c>
-      <c r="N19">
+      <c r="P19">
         <v>2.85267248150138</v>
       </c>
-      <c r="O19">
+      <c r="Q19">
         <v>10.3881624217992</v>
       </c>
-      <c r="P19">
+      <c r="R19">
         <v>-2.43871452073299</v>
       </c>
-      <c r="Q19">
+      <c r="S19">
         <v>0.374478042125702</v>
       </c>
-      <c r="R19">
+      <c r="T19">
         <v>11.2899126640813</v>
       </c>
-      <c r="S19">
+      <c r="U19">
         <v>277548941768.855</v>
       </c>
-      <c r="T19">
+      <c r="V19">
         <v>1.06599499526028</v>
       </c>
-      <c r="U19">
+      <c r="W19">
         <v>28.0120155631098</v>
       </c>
-      <c r="V19">
+      <c r="X19">
         <v>4.622</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:24">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -1698,52 +1818,58 @@
         <v>343583000000</v>
       </c>
       <c r="H20">
+        <v>14769862000000</v>
+      </c>
+      <c r="I20">
         <v>0.113587248160997</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>48570.0594269601</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>41.1</v>
       </c>
-      <c r="K20">
+      <c r="L20">
+        <v>15.9340757550748</v>
+      </c>
+      <c r="M20">
         <v>22.7876198166239</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>17.7131499265193</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>17.441943601098</v>
       </c>
-      <c r="N20">
+      <c r="P20">
         <v>3.839100296651</v>
       </c>
-      <c r="O20">
+      <c r="Q20">
         <v>8.713616781055951</v>
       </c>
-      <c r="P20">
+      <c r="R20">
         <v>-5.24151545897991</v>
       </c>
-      <c r="Q20">
+      <c r="S20">
         <v>0.5826595425605769</v>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>10.2761880916694</v>
       </c>
-      <c r="S20">
+      <c r="U20">
         <v>294045673779.627</v>
       </c>
-      <c r="T20">
+      <c r="V20">
         <v>1.07901356702484</v>
       </c>
-      <c r="U20">
+      <c r="W20">
         <v>29.8677875257061</v>
       </c>
-      <c r="V20">
+      <c r="X20">
         <v>5.784</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:24">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -1766,52 +1892,58 @@
         <v>312597000000</v>
       </c>
       <c r="H21">
+        <v>14478067000000</v>
+      </c>
+      <c r="I21">
         <v>-2.57650023225001</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>47194.9500893872</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>40.8</v>
       </c>
-      <c r="K21">
+      <c r="L21">
+        <v>16.8076926291334</v>
+      </c>
+      <c r="M21">
         <v>25.5765165335953</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>15.6666480407916</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>13.8273085764833</v>
       </c>
-      <c r="N21">
+      <c r="P21">
         <v>-0.355546266299747</v>
       </c>
-      <c r="O21">
+      <c r="Q21">
         <v>6.83788042145024</v>
       </c>
-      <c r="P21">
+      <c r="R21">
         <v>-10.1899701113415</v>
       </c>
-      <c r="Q21">
+      <c r="S21">
         <v>0.447313606739044</v>
       </c>
-      <c r="R21">
+      <c r="T21">
         <v>7.90351709244059</v>
       </c>
-      <c r="S21">
+      <c r="U21">
         <v>404098925258.352</v>
       </c>
-      <c r="T21">
+      <c r="V21">
         <v>1.92028077353965</v>
       </c>
-      <c r="U21">
+      <c r="W21">
         <v>24.759527635837</v>
       </c>
-      <c r="V21">
+      <c r="X21">
         <v>9.254</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:24">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -1834,52 +1966,58 @@
         <v>349828000000</v>
       </c>
       <c r="H22">
+        <v>15048971000000</v>
+      </c>
+      <c r="I22">
         <v>2.69519258234851</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>48642.6312088213</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>40.2</v>
       </c>
-      <c r="K22">
+      <c r="L22">
+        <v>16.6858385201221</v>
+      </c>
+      <c r="M22">
         <v>26.0545933672143</v>
       </c>
-      <c r="L22">
+      <c r="N22">
         <v>16.4034431324241</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>15.878527508625</v>
       </c>
-      <c r="N22">
+      <c r="P22">
         <v>1.6400434423899</v>
       </c>
-      <c r="O22">
+      <c r="Q22">
         <v>7.15792164762595</v>
       </c>
-      <c r="P22">
+      <c r="R22">
         <v>-9.99381153701472</v>
       </c>
-      <c r="Q22">
+      <c r="S22">
         <v>0.438403934240341</v>
       </c>
-      <c r="R22">
+      <c r="T22">
         <v>8.563222030263731</v>
       </c>
-      <c r="S22">
+      <c r="U22">
         <v>488928508742.44</v>
       </c>
-      <c r="T22">
+      <c r="V22">
         <v>2.00331890203891</v>
       </c>
-      <c r="U22">
+      <c r="W22">
         <v>28.2198829408336</v>
       </c>
-      <c r="V22">
+      <c r="X22">
         <v>9.632999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:24">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -1902,52 +2040,58 @@
         <v>436616000000</v>
       </c>
       <c r="H23">
+        <v>15599732000000</v>
+      </c>
+      <c r="I23">
         <v>1.56440685537306</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>50024.8812320773</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>41.2</v>
       </c>
-      <c r="K23">
+      <c r="L23">
+        <v>16.0984239985661</v>
+      </c>
+      <c r="M23">
         <v>25.3456995286842</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>16.6294350441405</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>17.2790147933311</v>
       </c>
-      <c r="N23">
+      <c r="P23">
         <v>3.156841568622</v>
       </c>
-      <c r="O23">
+      <c r="Q23">
         <v>8.21153762302025</v>
       </c>
-      <c r="P23">
+      <c r="R23">
         <v>-8.94621330674142</v>
       </c>
-      <c r="Q23">
+      <c r="S23">
         <v>0.591247260570526</v>
       </c>
-      <c r="R23">
+      <c r="T23">
         <v>9.53892861749163</v>
       </c>
-      <c r="S23">
+      <c r="U23">
         <v>537267041107.474</v>
       </c>
-      <c r="T23">
+      <c r="V23">
         <v>1.96135892377522</v>
       </c>
-      <c r="U23">
+      <c r="W23">
         <v>30.842478575914</v>
       </c>
-      <c r="V23">
+      <c r="X23">
         <v>8.949</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:24">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -1970,52 +2114,58 @@
         <v>377240000000</v>
       </c>
       <c r="H24">
+        <v>16253970000000</v>
+      </c>
+      <c r="I24">
         <v>2.289113386319</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>51708.3940614082</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>41.2</v>
       </c>
-      <c r="K24">
+      <c r="L24">
+        <v>15.4758499000552</v>
+      </c>
+      <c r="M24">
         <v>23.9119039840728</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>16.7477397829576</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>17.0377883064876</v>
       </c>
-      <c r="N24">
+      <c r="P24">
         <v>2.06933726526067</v>
       </c>
-      <c r="O24">
+      <c r="Q24">
         <v>8.17272283724602</v>
       </c>
-      <c r="P24">
+      <c r="R24">
         <v>-7.3043865590991</v>
       </c>
-      <c r="Q24">
+      <c r="S24">
         <v>0.6324421167373659</v>
       </c>
-      <c r="R24">
+      <c r="T24">
         <v>9.763917369110439</v>
       </c>
-      <c r="S24">
+      <c r="U24">
         <v>574268084132.447</v>
       </c>
-      <c r="T24">
+      <c r="V24">
         <v>2.04662420386995</v>
       </c>
-      <c r="U24">
+      <c r="W24">
         <v>30.681839575193</v>
       </c>
-      <c r="V24">
+      <c r="X24">
         <v>8.069000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:24">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -2038,52 +2188,58 @@
         <v>392796000000</v>
       </c>
       <c r="H25">
+        <v>16880683000000</v>
+      </c>
+      <c r="I25">
         <v>2.11783009786468</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>53297.3862901595</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>40.9</v>
       </c>
-      <c r="K25">
+      <c r="L25">
+        <v>14.9919526360397</v>
+      </c>
+      <c r="M25">
         <v>22.8814639786791</v>
       </c>
-      <c r="L25">
+      <c r="N25">
         <v>18.7407120908556</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>16.3878144030073</v>
       </c>
-      <c r="N25">
+      <c r="P25">
         <v>1.46483265562717</v>
       </c>
-      <c r="O25">
+      <c r="Q25">
         <v>7.63641114151764</v>
       </c>
-      <c r="P25">
+      <c r="R25">
         <v>-4.15034273198543</v>
       </c>
-      <c r="Q25">
+      <c r="S25">
         <v>0.643072605133057</v>
       </c>
-      <c r="R25">
+      <c r="T25">
         <v>10.4602254541478</v>
       </c>
-      <c r="S25">
+      <c r="U25">
         <v>448508920737.711</v>
       </c>
-      <c r="T25">
+      <c r="V25">
         <v>1.59421468829977</v>
       </c>
-      <c r="U25">
+      <c r="W25">
         <v>29.9413062848227</v>
       </c>
-      <c r="V25">
+      <c r="X25">
         <v>7.375</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:24">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -2106,52 +2262,58 @@
         <v>387529000000</v>
       </c>
       <c r="H26">
+        <v>17608138000000</v>
+      </c>
+      <c r="I26">
         <v>2.52381981372621</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>55153.3940182967</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>41.7</v>
       </c>
-      <c r="K26">
+      <c r="L26">
+        <v>14.5516578754664</v>
+      </c>
+      <c r="M26">
         <v>22.6100726834376</v>
       </c>
-      <c r="L26">
+      <c r="N26">
         <v>18.8588452680232</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>16.3983551242045</v>
       </c>
-      <c r="N26">
+      <c r="P26">
         <v>1.62222297740817</v>
       </c>
-      <c r="O26">
+      <c r="Q26">
         <v>7.85257698357646</v>
       </c>
-      <c r="P26">
+      <c r="R26">
         <v>-3.70170258774664</v>
       </c>
-      <c r="Q26">
+      <c r="S26">
         <v>0.582419633865356</v>
       </c>
-      <c r="R26">
+      <c r="T26">
         <v>10.8997481732594</v>
       </c>
-      <c r="S26">
+      <c r="U26">
         <v>434416188744.625</v>
       </c>
-      <c r="T26">
+      <c r="V26">
         <v>1.48004639876335</v>
       </c>
-      <c r="U26">
+      <c r="W26">
         <v>29.906569337428</v>
       </c>
-      <c r="V26">
+      <c r="X26">
         <v>6.168</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:24">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -2174,52 +2336,58 @@
         <v>302071000000</v>
       </c>
       <c r="H27">
+        <v>18295019000000</v>
+      </c>
+      <c r="I27">
         <v>2.94555045599772</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>56849.4697923159</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>41.5</v>
       </c>
-      <c r="K27">
+      <c r="L27">
+        <v>14.2333167295426</v>
+      </c>
+      <c r="M27">
         <v>22.3735356601707</v>
       </c>
-      <c r="L27">
+      <c r="N27">
         <v>18.9953587913738</v>
       </c>
-      <c r="M27">
+      <c r="O27">
         <v>15.2770653039497</v>
       </c>
-      <c r="N27">
+      <c r="P27">
         <v>0.118627135552451</v>
       </c>
-      <c r="O27">
+      <c r="Q27">
         <v>7.48353395911593</v>
       </c>
-      <c r="P27">
+      <c r="R27">
         <v>-3.19804149971093</v>
       </c>
-      <c r="Q27">
+      <c r="S27">
         <v>0.662890195846558</v>
       </c>
-      <c r="R27">
+      <c r="T27">
         <v>11.1828279598944</v>
       </c>
-      <c r="S27">
+      <c r="U27">
         <v>383728497570.133</v>
       </c>
-      <c r="T27">
+      <c r="V27">
         <v>1.34985594012155</v>
       </c>
-      <c r="U27">
+      <c r="W27">
         <v>27.6882139340768</v>
       </c>
-      <c r="V27">
+      <c r="X27">
         <v>5.28</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:24">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -2242,52 +2410,58 @@
         <v>299815000000</v>
       </c>
       <c r="H28">
+        <v>18804913000000</v>
+      </c>
+      <c r="I28">
         <v>1.81945147620522</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>57976.628204291</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>41.3</v>
       </c>
-      <c r="K28">
+      <c r="L28">
+        <v>14.1100041249858</v>
+      </c>
+      <c r="M28">
         <v>22.4159218391492</v>
       </c>
-      <c r="L28">
+      <c r="N28">
         <v>18.540821220497</v>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>14.5644385592212</v>
       </c>
-      <c r="N28">
+      <c r="P28">
         <v>1.26158320570536</v>
       </c>
-      <c r="O28">
+      <c r="Q28">
         <v>8.20032602229035</v>
       </c>
-      <c r="P28">
+      <c r="R28">
         <v>-3.83020224555147</v>
       </c>
-      <c r="Q28">
+      <c r="S28">
         <v>0.385635316371918</v>
       </c>
-      <c r="R28">
+      <c r="T28">
         <v>10.8545149876524</v>
       </c>
-      <c r="S28">
+      <c r="U28">
         <v>405942428719.749</v>
       </c>
-      <c r="T28">
+      <c r="V28">
         <v>1.44075451131827</v>
       </c>
-      <c r="U28">
+      <c r="W28">
         <v>26.4525977865465</v>
       </c>
-      <c r="V28">
+      <c r="X28">
         <v>4.869</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:24">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -2310,52 +2484,58 @@
         <v>409413000000</v>
       </c>
       <c r="H29">
+        <v>19612102000000</v>
+      </c>
+      <c r="I29">
         <v>2.45762230175086</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>60047.7190728307</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>41.4</v>
       </c>
-      <c r="K29">
+      <c r="L29">
+        <v>13.8471337748498</v>
+      </c>
+      <c r="M29">
         <v>22.1406996557534</v>
       </c>
-      <c r="L29">
+      <c r="N29">
         <v>19.2095273622379</v>
       </c>
-      <c r="M29">
+      <c r="O29">
         <v>14.9478571955214</v>
       </c>
-      <c r="N29">
+      <c r="P29">
         <v>2.13011000365961</v>
       </c>
-      <c r="O29">
+      <c r="Q29">
         <v>8.49884136280661</v>
       </c>
-      <c r="P29">
+      <c r="R29">
         <v>-2.94418313753416</v>
       </c>
-      <c r="Q29">
+      <c r="S29">
         <v>0.262138307094574</v>
       </c>
-      <c r="R29">
+      <c r="T29">
         <v>11.5038867327939</v>
       </c>
-      <c r="S29">
+      <c r="U29">
         <v>451285263406.24</v>
       </c>
-      <c r="T29">
+      <c r="V29">
         <v>1.48411996805483</v>
       </c>
-      <c r="U29">
+      <c r="W29">
         <v>27.1253382222874</v>
       </c>
-      <c r="V29">
+      <c r="X29">
         <v>4.355</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:24">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -2378,52 +2558,58 @@
         <v>-130720000000</v>
       </c>
       <c r="H30">
+        <v>20656516000000</v>
+      </c>
+      <c r="I30">
         <v>2.96650506916596</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>62875.6661382728</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>41.8</v>
       </c>
-      <c r="K30">
+      <c r="L30">
+        <v>13.8442126445718</v>
+      </c>
+      <c r="M30">
         <v>22.1694791125473</v>
       </c>
-      <c r="L30">
+      <c r="N30">
         <v>17.4793585714067</v>
       </c>
-      <c r="M30">
+      <c r="O30">
         <v>15.1582483706352</v>
       </c>
-      <c r="N30">
+      <c r="P30">
         <v>2.44258329692817</v>
       </c>
-      <c r="O30">
+      <c r="Q30">
         <v>9.670920605610901</v>
       </c>
-      <c r="P30">
+      <c r="R30">
         <v>-4.77899854941656</v>
       </c>
-      <c r="Q30">
+      <c r="S30">
         <v>0.38623908162117</v>
       </c>
-      <c r="R30">
+      <c r="T30">
         <v>9.929538940642271</v>
       </c>
-      <c r="S30">
+      <c r="U30">
         <v>449907088828.546</v>
       </c>
-      <c r="T30">
+      <c r="V30">
         <v>1.3600015179599</v>
       </c>
-      <c r="U30">
+      <c r="W30">
         <v>27.4453591302618</v>
       </c>
-      <c r="V30">
+      <c r="X30">
         <v>3.896</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:24">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -2446,52 +2632,58 @@
         <v>114927000000</v>
       </c>
       <c r="H31">
+        <v>21539982000000</v>
+      </c>
+      <c r="I31">
         <v>2.58382533018889</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>65227.9565911038</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>41.9</v>
       </c>
-      <c r="K31">
+      <c r="L31">
+        <v>13.9835585749329</v>
+      </c>
+      <c r="M31">
         <v>22.514337755714</v>
       </c>
-      <c r="L31">
+      <c r="N31">
         <v>17.2913779593688</v>
       </c>
-      <c r="M31">
+      <c r="O31">
         <v>14.4692832148142</v>
       </c>
-      <c r="N31">
+      <c r="P31">
         <v>1.81221007526021</v>
       </c>
-      <c r="O31">
+      <c r="Q31">
         <v>9.82845065710065</v>
       </c>
-      <c r="P31">
+      <c r="R31">
         <v>-5.35878674364723</v>
       </c>
-      <c r="Q31">
+      <c r="S31">
         <v>0.118298575282097</v>
       </c>
-      <c r="R31">
+      <c r="T31">
         <v>9.88478959731721</v>
       </c>
-      <c r="S31">
+      <c r="U31">
         <v>516700583371.247</v>
       </c>
-      <c r="T31">
+      <c r="V31">
         <v>1.54805985915951</v>
       </c>
-      <c r="U31">
+      <c r="W31">
         <v>26.2584806245428</v>
       </c>
-      <c r="V31">
+      <c r="X31">
         <v>3.669</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:24">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -2514,52 +2706,58 @@
         <v>282331000000</v>
       </c>
       <c r="H32">
+        <v>21354105000000</v>
+      </c>
+      <c r="I32">
         <v>-2.16302913866512</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>64401.5074354212</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>40</v>
       </c>
-      <c r="K32">
+      <c r="L32">
+        <v>14.8957448696632</v>
+      </c>
+      <c r="M32">
         <v>31.8281473281133</v>
       </c>
-      <c r="L32">
+      <c r="N32">
         <v>17.708696290479</v>
       </c>
-      <c r="M32">
+      <c r="O32">
         <v>13.0061222420701</v>
       </c>
-      <c r="N32">
+      <c r="P32">
         <v>1.23358439630629</v>
       </c>
-      <c r="O32">
+      <c r="Q32">
         <v>6.06749005681651</v>
       </c>
-      <c r="P32">
+      <c r="R32">
         <v>-14.3606964562551</v>
       </c>
-      <c r="Q32">
+      <c r="S32">
         <v>-0.0278997328132391</v>
       </c>
-      <c r="R32">
+      <c r="T32">
         <v>10.1534220235407</v>
       </c>
-      <c r="S32">
+      <c r="U32">
         <v>628369715338.322</v>
       </c>
-      <c r="T32">
+      <c r="V32">
         <v>2.09737678529136</v>
       </c>
-      <c r="U32">
+      <c r="W32">
         <v>23.0797778694073</v>
       </c>
-      <c r="V32">
+      <c r="X32">
         <v>8.055</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:24">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -2582,52 +2780,58 @@
         <v>342151000000</v>
       </c>
       <c r="H33">
+        <v>23681171000000</v>
+      </c>
+      <c r="I33">
         <v>6.05505293304556</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>71307.40172772179</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>39.7</v>
       </c>
-      <c r="K33">
+      <c r="L33">
+        <v>14.2530325041781</v>
+      </c>
+      <c r="M33">
         <v>31.3034760823272</v>
       </c>
-      <c r="L33">
+      <c r="N33">
         <v>18.808352424802</v>
       </c>
-      <c r="M33">
+      <c r="O33">
         <v>14.422677831261</v>
       </c>
-      <c r="N33">
+      <c r="P33">
         <v>4.69785886363742</v>
       </c>
-      <c r="O33">
+      <c r="Q33">
         <v>6.84847789022078</v>
       </c>
-      <c r="P33">
+      <c r="R33">
         <v>-12.6578436513971</v>
       </c>
-      <c r="Q33">
+      <c r="S33">
         <v>-0.0144246527925134</v>
       </c>
-      <c r="R33">
+      <c r="T33">
         <v>11.394678497951</v>
       </c>
-      <c r="S33">
+      <c r="U33">
         <v>716152260973.7111</v>
       </c>
-      <c r="T33">
+      <c r="V33">
         <v>1.97445270826071</v>
       </c>
-      <c r="U33">
+      <c r="W33">
         <v>25.2136560307765</v>
       </c>
-      <c r="V33">
+      <c r="X33">
         <v>5.349</v>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:24">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -2650,52 +2854,58 @@
         <v>388847000000</v>
       </c>
       <c r="H34">
+        <v>26006893000000</v>
+      </c>
+      <c r="I34">
         <v>2.5123753198332</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>77860.9112908848</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>41.7</v>
       </c>
-      <c r="K34">
+      <c r="L34">
+        <v>13.7137950311865</v>
+      </c>
+      <c r="M34">
         <v>24.658458048026</v>
       </c>
-      <c r="L34">
+      <c r="N34">
         <v>19.9277753017248</v>
       </c>
-      <c r="M34">
+      <c r="O34">
         <v>15.2894619130397</v>
       </c>
-      <c r="N34">
+      <c r="P34">
         <v>8.00279982052121</v>
       </c>
-      <c r="O34">
+      <c r="Q34">
         <v>10.8355382124539</v>
       </c>
-      <c r="P34">
+      <c r="R34">
         <v>-4.41897730728542</v>
       </c>
-      <c r="Q34">
+      <c r="S34">
         <v>0.00870068650692701</v>
       </c>
-      <c r="R34">
+      <c r="T34">
         <v>12.5989036829582</v>
       </c>
-      <c r="S34">
+      <c r="U34">
         <v>706644215998.894</v>
       </c>
-      <c r="T34">
+      <c r="V34">
         <v>1.67967044769329</v>
       </c>
-      <c r="U34">
+      <c r="W34">
         <v>26.891689830077</v>
       </c>
-      <c r="V34">
+      <c r="X34">
         <v>3.65</v>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:24">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -2718,52 +2928,58 @@
         <v>351085000000</v>
       </c>
       <c r="H35">
+        <v>27720709000000</v>
+      </c>
+      <c r="I35">
         <v>2.88755600905984</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>82304.6204272866</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>41.8</v>
       </c>
-      <c r="K35">
+      <c r="L35">
+        <v>13.4338338893136</v>
+      </c>
+      <c r="M35">
         <v>24.5133766239529</v>
       </c>
-      <c r="L35">
+      <c r="N35">
         <v>17.5921957840256</v>
       </c>
-      <c r="M35">
+      <c r="O35">
         <v>13.8878518583345</v>
       </c>
-      <c r="N35">
+      <c r="P35">
         <v>4.11633838374488</v>
       </c>
-      <c r="O35">
+      <c r="Q35">
         <v>12.9081122139776</v>
       </c>
-      <c r="P35">
+      <c r="R35">
         <v>-7.14191076425931</v>
       </c>
-      <c r="Q35">
+      <c r="S35">
         <v>0.029424749314785</v>
       </c>
-      <c r="R35">
+      <c r="T35">
         <v>10.6459127722888</v>
       </c>
-      <c r="S35">
+      <c r="U35">
         <v>773426187289.1281</v>
       </c>
-      <c r="T35">
+      <c r="V35">
         <v>1.79263382538627</v>
       </c>
-      <c r="U35">
+      <c r="W35">
         <v>24.8993631439946</v>
       </c>
-      <c r="V35">
+      <c r="X35">
         <v>3.638</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:24">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -2780,27 +2996,33 @@
         <v>322167000000</v>
       </c>
       <c r="H36">
+        <v>29184890000000</v>
+      </c>
+      <c r="I36">
         <v>2.79619035621393</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>85809.90038463561</v>
       </c>
-      <c r="M36">
+      <c r="L36">
+        <v>13.4202664460959</v>
+      </c>
+      <c r="O36">
         <v>13.9911166360401</v>
       </c>
-      <c r="N36">
+      <c r="P36">
         <v>2.94952520485207</v>
       </c>
-      <c r="S36">
+      <c r="U36">
         <v>910036546651.5</v>
       </c>
-      <c r="T36">
+      <c r="V36">
         <v>1.94032058064746</v>
       </c>
-      <c r="U36">
+      <c r="W36">
         <v>24.8879916970734</v>
       </c>
-      <c r="V36">
+      <c r="X36">
         <v>4.106</v>
       </c>
     </row>

--- a/USA_WB_timeseries.xlsx
+++ b/USA_WB_timeseries.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beldjenna/Desktop/Rating Algo/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEBE3F8-8485-A047-AB5F-7533A1B1D803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -73,8 +67,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,18 +85,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -132,33 +120,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +175,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,7 +209,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,10 +243,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,11 +418,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -495,24 +472,24 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
       <c r="B2">
-        <v>1.6035974025726301</v>
+        <v>1.60359740257263</v>
       </c>
       <c r="C2">
-        <v>-3.9208846163751399</v>
+        <v>-3.92088461637514</v>
       </c>
       <c r="D2">
-        <v>33.267641873652302</v>
+        <v>33.2676418736523</v>
       </c>
       <c r="E2">
-        <v>10.692772729791299</v>
+        <v>10.6927727297913</v>
       </c>
       <c r="F2">
-        <v>4.0775857600695398</v>
+        <v>4.07758576006954</v>
       </c>
       <c r="G2">
         <v>36329.9702595751</v>
@@ -521,52 +498,51 @@
         <v>17.9265301408103</v>
       </c>
       <c r="I2">
-        <v>20.576137708966002</v>
+        <v>20.576137708966</v>
       </c>
       <c r="J2">
-        <v>14.410212827062299</v>
+        <v>14.4102128270623</v>
       </c>
       <c r="K2">
-        <v>3.3768572714992899</v>
+        <v>3.37685727149929</v>
       </c>
       <c r="L2">
-        <v>12.862149278422301</v>
+        <v>12.8621492784223</v>
       </c>
       <c r="M2">
-        <v>2.2336462018356902</v>
+        <v>2.23364620183569</v>
       </c>
       <c r="N2">
         <v>1.08280909061432</v>
       </c>
       <c r="O2">
-        <v>12.970795297841599</v>
+        <v>12.9707952978416</v>
       </c>
       <c r="P2">
         <v>25.1029855568536</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3" s="2"/>
       <c r="C3">
-        <v>-3.7240752607582199</v>
+        <v>-3.72407526075822</v>
       </c>
       <c r="D3">
         <v>53.5</v>
       </c>
       <c r="E3">
-        <v>9.7034482087339704</v>
+        <v>9.70344820873397</v>
       </c>
       <c r="F3">
-        <v>0.95553834188667996</v>
+        <v>0.95553834188668</v>
       </c>
       <c r="G3">
-        <v>37133.620397351697</v>
+        <v>37133.6203973517</v>
       </c>
       <c r="H3">
-        <v>19.509764240527399</v>
+        <v>19.5097642405274</v>
       </c>
       <c r="I3">
         <v>19.5089146789777</v>
@@ -575,23 +551,22 @@
         <v>13.2637348067635</v>
       </c>
       <c r="K3">
-        <v>2.8261711188540701</v>
+        <v>2.82617111885407</v>
       </c>
       <c r="L3">
-        <v>12.525087073955699</v>
+        <v>12.5250870739557</v>
       </c>
       <c r="M3">
-        <v>1.3981382789470601E-2</v>
-      </c>
-      <c r="N3" s="2"/>
+        <v>0.0139813827894706</v>
+      </c>
       <c r="O3">
         <v>11.8577047719749</v>
       </c>
       <c r="P3">
-        <v>22.967183015497501</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+        <v>22.9671830154975</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
@@ -599,22 +574,22 @@
         <v>1.87359666824341</v>
       </c>
       <c r="C4">
-        <v>-4.1733415023440203</v>
+        <v>-4.17334150234402</v>
       </c>
       <c r="D4">
         <v>55.9</v>
       </c>
       <c r="E4">
-        <v>9.1313856537971798</v>
+        <v>9.13138565379718</v>
       </c>
       <c r="F4">
         <v>1.7004473278454</v>
       </c>
       <c r="G4">
-        <v>37997.742430024198</v>
+        <v>37997.7424300242</v>
       </c>
       <c r="H4">
-        <v>20.084018750661102</v>
+        <v>20.0840187506611</v>
       </c>
       <c r="I4">
         <v>17.3842220243409</v>
@@ -623,7 +598,7 @@
         <v>13.1549985598093</v>
       </c>
       <c r="K4">
-        <v>1.5860316265060099</v>
+        <v>1.58603162650601</v>
       </c>
       <c r="L4">
         <v>10.372518210786</v>
@@ -632,16 +607,16 @@
         <v>-2.84500802810257</v>
       </c>
       <c r="N4">
-        <v>0.28547692298889199</v>
+        <v>0.285476922988892</v>
       </c>
       <c r="O4">
-        <v>9.8680166762008401</v>
+        <v>9.86801667620084</v>
       </c>
       <c r="P4">
         <v>22.2863842136065</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
@@ -649,49 +624,49 @@
         <v>1.7044905424118</v>
       </c>
       <c r="C5">
-        <v>-4.5589776937882096</v>
+        <v>-4.55897769378821</v>
       </c>
       <c r="D5">
         <v>59</v>
       </c>
       <c r="E5">
-        <v>9.0356524054135399</v>
+        <v>9.03565240541354</v>
       </c>
       <c r="F5">
-        <v>2.7956059652123302</v>
+        <v>2.79560596521233</v>
       </c>
       <c r="G5">
         <v>39490.3023903176</v>
       </c>
       <c r="H5">
-        <v>20.660618254345799</v>
+        <v>20.6606182543458</v>
       </c>
       <c r="I5">
-        <v>16.777429308380899</v>
+        <v>16.7774293083809</v>
       </c>
       <c r="J5">
-        <v>13.591644881267801</v>
+        <v>13.5916448812678</v>
       </c>
       <c r="K5">
-        <v>2.2700949733611502</v>
+        <v>2.27009497336115</v>
       </c>
       <c r="L5">
         <v>8.98132611038214</v>
       </c>
       <c r="M5">
-        <v>-4.0784239445901704</v>
+        <v>-4.07842394459017</v>
       </c>
       <c r="N5">
-        <v>8.0440349876880604E-2</v>
+        <v>0.0804403498768806</v>
       </c>
       <c r="O5">
         <v>9.3906925792894</v>
       </c>
       <c r="P5">
-        <v>22.627297286681301</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+        <v>22.6272972866813</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
@@ -699,19 +674,19 @@
         <v>1.81070196628571</v>
       </c>
       <c r="C6">
-        <v>-5.2048522426913699</v>
+        <v>-5.20485224269137</v>
       </c>
       <c r="D6">
-        <v>66.400000000000006</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E6">
-        <v>9.6287478730798792</v>
+        <v>9.628747873079879</v>
       </c>
       <c r="F6">
-        <v>3.8477716942415299</v>
+        <v>3.84777169424153</v>
       </c>
       <c r="G6">
-        <v>41724.641198261401</v>
+        <v>41724.6411982614</v>
       </c>
       <c r="H6">
         <v>20.4485309067645</v>
@@ -723,25 +698,25 @@
         <v>14.8193087841105</v>
       </c>
       <c r="K6">
-        <v>2.6772366930917202</v>
+        <v>2.67723669309172</v>
       </c>
       <c r="L6">
-        <v>8.8387167094748502</v>
+        <v>8.83871670947485</v>
       </c>
       <c r="M6">
-        <v>-3.8268486484132702</v>
+        <v>-3.82684864841327</v>
       </c>
       <c r="N6">
         <v>-0.233039826154709</v>
       </c>
       <c r="O6">
-        <v>9.5374707911700796</v>
+        <v>9.53747079117008</v>
       </c>
       <c r="P6">
-        <v>24.448056657190399</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+        <v>24.4480566571904</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
@@ -749,19 +724,19 @@
         <v>1.53672695159912</v>
       </c>
       <c r="C7">
-        <v>-5.7459826705586199</v>
+        <v>-5.74598267055862</v>
       </c>
       <c r="D7">
         <v>65.8</v>
       </c>
       <c r="E7">
-        <v>9.9820564103755807</v>
+        <v>9.982056410375581</v>
       </c>
       <c r="F7">
-        <v>3.4835499354455899</v>
+        <v>3.48354993544559</v>
       </c>
       <c r="G7">
-        <v>44123.399647002603</v>
+        <v>44123.3996470026</v>
       </c>
       <c r="H7">
         <v>20.7451064662954</v>
@@ -770,28 +745,28 @@
         <v>17.928590234506</v>
       </c>
       <c r="J7">
-        <v>15.656500933301301</v>
+        <v>15.6565009333013</v>
       </c>
       <c r="K7">
-        <v>3.3927468454955001</v>
+        <v>3.3927468454955</v>
       </c>
       <c r="L7">
         <v>9.51690747854534</v>
       </c>
       <c r="M7">
-        <v>-3.0366463517653699</v>
+        <v>-3.03664635176537</v>
       </c>
       <c r="N7">
-        <v>-6.05432577431202E-2</v>
+        <v>-0.0605432577431202</v>
       </c>
       <c r="O7">
         <v>10.6817329318669</v>
       </c>
       <c r="P7">
-        <v>25.638557343676901</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+        <v>25.6385573436769</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
@@ -799,7 +774,7 @@
         <v>1.34489262104034</v>
       </c>
       <c r="C8">
-        <v>-5.9110209102286904</v>
+        <v>-5.91102091022869</v>
       </c>
       <c r="D8">
         <v>64.5</v>
@@ -808,40 +783,40 @@
         <v>10.641389509223</v>
       </c>
       <c r="F8">
-        <v>2.7845396381789098</v>
+        <v>2.78453963817891</v>
       </c>
       <c r="G8">
-        <v>46301.987648551898</v>
+        <v>46301.9876485519</v>
       </c>
       <c r="H8">
-        <v>20.595141008526401</v>
+        <v>20.5951410085264</v>
       </c>
       <c r="I8">
         <v>18.6287129540606</v>
       </c>
       <c r="J8">
-        <v>16.333896296667302</v>
+        <v>16.3338962966673</v>
       </c>
       <c r="K8">
-        <v>3.2259441007040399</v>
+        <v>3.22594410070404</v>
       </c>
       <c r="L8">
-        <v>9.8609311481641502</v>
+        <v>9.86093114816415</v>
       </c>
       <c r="M8">
-        <v>-2.1057229361945899</v>
+        <v>-2.10572293619459</v>
       </c>
       <c r="N8">
-        <v>0.49083548784255998</v>
+        <v>0.49083548784256</v>
       </c>
       <c r="O8">
-        <v>11.310478899080801</v>
+        <v>11.3104788990808</v>
       </c>
       <c r="P8">
-        <v>26.975285805890302</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+        <v>26.9752858058903</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
@@ -849,19 +824,19 @@
         <v>1.37706923484802</v>
       </c>
       <c r="C9">
-        <v>-5.0887273573416101</v>
+        <v>-5.08872735734161</v>
       </c>
       <c r="D9">
-        <v>64.900000000000006</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E9">
         <v>11.4637892950146</v>
       </c>
       <c r="F9">
-        <v>2.0038582990915801</v>
+        <v>2.00385829909158</v>
       </c>
       <c r="G9">
-        <v>48050.227412195003</v>
+        <v>48050.227412195</v>
       </c>
       <c r="H9">
         <v>20.8646436963685</v>
@@ -870,28 +845,28 @@
         <v>18.6567829386134</v>
       </c>
       <c r="J9">
-        <v>16.548226268095299</v>
+        <v>16.5482262680953</v>
       </c>
       <c r="K9">
-        <v>2.8526724815013802</v>
+        <v>2.85267248150138</v>
       </c>
       <c r="L9">
-        <v>10.388162421799199</v>
+        <v>10.3881624217992</v>
       </c>
       <c r="M9">
-        <v>-2.4387145207329901</v>
+        <v>-2.43871452073299</v>
       </c>
       <c r="N9">
-        <v>0.37447804212570202</v>
+        <v>0.374478042125702</v>
       </c>
       <c r="O9">
-        <v>11.289912664081299</v>
+        <v>11.2899126640813</v>
       </c>
       <c r="P9">
-        <v>28.012015563109799</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+        <v>28.0120155631098</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
@@ -899,22 +874,22 @@
         <v>1.43763339519501</v>
       </c>
       <c r="C10">
-        <v>-4.7158599044459599</v>
+        <v>-4.71585990444596</v>
       </c>
       <c r="D10">
         <v>73.8</v>
       </c>
       <c r="E10">
-        <v>12.425843924608101</v>
+        <v>12.4258439246081</v>
       </c>
       <c r="F10">
         <v>0.113587248160997</v>
       </c>
       <c r="G10">
-        <v>48570.059426960099</v>
+        <v>48570.0594269601</v>
       </c>
       <c r="H10">
-        <v>22.787619816623899</v>
+        <v>22.7876198166239</v>
       </c>
       <c r="I10">
         <v>17.7131499265193</v>
@@ -923,25 +898,25 @@
         <v>17.441943601098</v>
       </c>
       <c r="K10">
-        <v>3.8391002966509999</v>
+        <v>3.839100296651</v>
       </c>
       <c r="L10">
-        <v>8.7136167810559506</v>
+        <v>8.713616781055951</v>
       </c>
       <c r="M10">
-        <v>-5.2415154589799098</v>
+        <v>-5.24151545897991</v>
       </c>
       <c r="N10">
-        <v>0.58265954256057695</v>
+        <v>0.5826595425605769</v>
       </c>
       <c r="O10">
         <v>10.2761880916694</v>
       </c>
       <c r="P10">
-        <v>29.867787525706099</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+        <v>29.8677875257061</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
@@ -949,49 +924,49 @@
         <v>1.28647637367249</v>
       </c>
       <c r="C11">
-        <v>-2.6228363220034798</v>
+        <v>-2.62283632200348</v>
       </c>
       <c r="D11">
-        <v>87.1</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="E11">
-        <v>10.932219059353701</v>
+        <v>10.9322190593537</v>
       </c>
       <c r="F11">
-        <v>-2.5765002322500101</v>
+        <v>-2.57650023225001</v>
       </c>
       <c r="G11">
-        <v>47194.950089387203</v>
+        <v>47194.9500893872</v>
       </c>
       <c r="H11">
-        <v>25.576516533595299</v>
+        <v>25.5765165335953</v>
       </c>
       <c r="I11">
         <v>15.6666480407916</v>
       </c>
       <c r="J11">
-        <v>13.827308576483301</v>
+        <v>13.8273085764833</v>
       </c>
       <c r="K11">
         <v>-0.355546266299747</v>
       </c>
       <c r="L11">
-        <v>6.8378804214502402</v>
+        <v>6.83788042145024</v>
       </c>
       <c r="M11">
         <v>-10.1899701113415</v>
       </c>
       <c r="N11">
-        <v>0.44731360673904402</v>
+        <v>0.447313606739044</v>
       </c>
       <c r="O11">
-        <v>7.9035170924405902</v>
+        <v>7.90351709244059</v>
       </c>
       <c r="P11">
-        <v>24.759527635836999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+        <v>24.759527635837</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
@@ -999,25 +974,25 @@
         <v>1.26525807380676</v>
       </c>
       <c r="C12">
-        <v>-2.8706414544888199</v>
+        <v>-2.87064145448882</v>
       </c>
       <c r="D12">
-        <v>95.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="E12">
         <v>12.3413554322086</v>
       </c>
       <c r="F12">
-        <v>2.6951925823485099</v>
+        <v>2.69519258234851</v>
       </c>
       <c r="G12">
-        <v>48642.631208821302</v>
+        <v>48642.6312088213</v>
       </c>
       <c r="H12">
-        <v>26.054593367214299</v>
+        <v>26.0545933672143</v>
       </c>
       <c r="I12">
-        <v>16.403443132424101</v>
+        <v>16.4034431324241</v>
       </c>
       <c r="J12">
         <v>15.878527508625</v>
@@ -1026,22 +1001,22 @@
         <v>1.6400434423899</v>
       </c>
       <c r="L12">
-        <v>7.1579216476259502</v>
+        <v>7.15792164762595</v>
       </c>
       <c r="M12">
-        <v>-9.9938115370147198</v>
+        <v>-9.99381153701472</v>
       </c>
       <c r="N12">
-        <v>0.43840393424034102</v>
+        <v>0.438403934240341</v>
       </c>
       <c r="O12">
-        <v>8.5632220302637307</v>
+        <v>8.563222030263731</v>
       </c>
       <c r="P12">
         <v>28.2198829408336</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
@@ -1049,7 +1024,7 @@
         <v>1.26211905479431</v>
       </c>
       <c r="C13">
-        <v>-2.9186206532266099</v>
+        <v>-2.91862065322661</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -1058,7 +1033,7 @@
         <v>13.5634637825829</v>
       </c>
       <c r="F13">
-        <v>1.5644068553730599</v>
+        <v>1.56440685537306</v>
       </c>
       <c r="G13">
         <v>50024.8812320773</v>
@@ -1073,25 +1048,25 @@
         <v>17.2790147933311</v>
       </c>
       <c r="K13">
-        <v>3.1568415686220002</v>
+        <v>3.156841568622</v>
       </c>
       <c r="L13">
-        <v>8.2115376230202504</v>
+        <v>8.21153762302025</v>
       </c>
       <c r="M13">
         <v>-8.94621330674142</v>
       </c>
       <c r="N13">
-        <v>0.59124726057052601</v>
+        <v>0.591247260570526</v>
       </c>
       <c r="O13">
-        <v>9.5389286174916297</v>
+        <v>9.53892861749163</v>
       </c>
       <c r="P13">
-        <v>30.842478575914001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+        <v>30.842478575914</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
@@ -1099,7 +1074,7 @@
         <v>1.40279400348663</v>
       </c>
       <c r="C14">
-        <v>-2.5723684736713599</v>
+        <v>-2.57236847367136</v>
       </c>
       <c r="D14">
         <v>103.7</v>
@@ -1108,40 +1083,40 @@
         <v>13.6440512687054</v>
       </c>
       <c r="F14">
-        <v>2.2891133863189999</v>
+        <v>2.289113386319</v>
       </c>
       <c r="G14">
-        <v>51708.394061408202</v>
+        <v>51708.3940614082</v>
       </c>
       <c r="H14">
-        <v>23.911903984072801</v>
+        <v>23.9119039840728</v>
       </c>
       <c r="I14">
-        <v>16.747739782957598</v>
+        <v>16.7477397829576</v>
       </c>
       <c r="J14">
-        <v>17.037788306487599</v>
+        <v>17.0377883064876</v>
       </c>
       <c r="K14">
-        <v>2.0693372652606699</v>
+        <v>2.06933726526067</v>
       </c>
       <c r="L14">
-        <v>8.1727228372460203</v>
+        <v>8.17272283724602</v>
       </c>
       <c r="M14">
-        <v>-7.3043865590991004</v>
+        <v>-7.3043865590991</v>
       </c>
       <c r="N14">
-        <v>0.63244211673736594</v>
+        <v>0.6324421167373659</v>
       </c>
       <c r="O14">
-        <v>9.7639173691104393</v>
+        <v>9.763917369110439</v>
       </c>
       <c r="P14">
-        <v>30.681839575192999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+        <v>30.681839575193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
@@ -1149,7 +1124,7 @@
         <v>1.30592489242554</v>
       </c>
       <c r="C15">
-        <v>-2.0109079709630202</v>
+        <v>-2.01090797096302</v>
       </c>
       <c r="D15">
         <v>105</v>
@@ -1161,45 +1136,45 @@
         <v>2.11783009786468</v>
       </c>
       <c r="G15">
-        <v>53297.386290159498</v>
+        <v>53297.3862901595</v>
       </c>
       <c r="H15">
-        <v>22.881463978679101</v>
+        <v>22.8814639786791</v>
       </c>
       <c r="I15">
-        <v>18.740712090855599</v>
+        <v>18.7407120908556</v>
       </c>
       <c r="J15">
-        <v>16.387814403007301</v>
+        <v>16.3878144030073</v>
       </c>
       <c r="K15">
         <v>1.46483265562717</v>
       </c>
       <c r="L15">
-        <v>7.6364111415176401</v>
+        <v>7.63641114151764</v>
       </c>
       <c r="M15">
-        <v>-4.1503427319854298</v>
+        <v>-4.15034273198543</v>
       </c>
       <c r="N15">
-        <v>0.64307260513305697</v>
+        <v>0.643072605133057</v>
       </c>
       <c r="O15">
         <v>10.4602254541478</v>
       </c>
       <c r="P15">
-        <v>29.941306284822701</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+        <v>29.9413062848227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
-        <v>1.3713780641555799</v>
+        <v>1.37137806415558</v>
       </c>
       <c r="C16">
-        <v>-2.1011761720631701</v>
+        <v>-2.10117617206317</v>
       </c>
       <c r="D16">
         <v>104.9</v>
@@ -1211,13 +1186,13 @@
         <v>2.52381981372621</v>
       </c>
       <c r="G16">
-        <v>55153.394018296698</v>
+        <v>55153.3940182967</v>
       </c>
       <c r="H16">
         <v>22.6100726834376</v>
       </c>
       <c r="I16">
-        <v>18.858845268023199</v>
+        <v>18.8588452680232</v>
       </c>
       <c r="J16">
         <v>16.3983551242045</v>
@@ -1226,10 +1201,10 @@
         <v>1.62222297740817</v>
       </c>
       <c r="L16">
-        <v>7.8525769835764603</v>
+        <v>7.85257698357646</v>
       </c>
       <c r="M16">
-        <v>-3.7017025877466398</v>
+        <v>-3.70170258774664</v>
       </c>
       <c r="N16">
         <v>0.582419633865356</v>
@@ -1238,10 +1213,10 @@
         <v>10.8997481732594</v>
       </c>
       <c r="P16">
-        <v>29.906569337427999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+        <v>29.906569337428</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
@@ -1249,7 +1224,7 @@
         <v>1.35772120952606</v>
       </c>
       <c r="C17">
-        <v>-2.2325584903737998</v>
+        <v>-2.2325584903738</v>
       </c>
       <c r="D17">
         <v>105.4</v>
@@ -1258,13 +1233,13 @@
         <v>12.4111486301271</v>
       </c>
       <c r="F17">
-        <v>2.9455504559977199</v>
+        <v>2.94555045599772</v>
       </c>
       <c r="G17">
-        <v>56849.469792315896</v>
+        <v>56849.4697923159</v>
       </c>
       <c r="H17">
-        <v>22.373535660170699</v>
+        <v>22.3735356601707</v>
       </c>
       <c r="I17">
         <v>18.9953587913738</v>
@@ -1276,27 +1251,27 @@
         <v>0.118627135552451</v>
       </c>
       <c r="L17">
-        <v>7.4835339591159302</v>
+        <v>7.48353395911593</v>
       </c>
       <c r="M17">
-        <v>-3.1980414997109299</v>
+        <v>-3.19804149971093</v>
       </c>
       <c r="N17">
-        <v>0.66289019584655795</v>
+        <v>0.662890195846558</v>
       </c>
       <c r="O17">
         <v>11.1828279598944</v>
       </c>
       <c r="P17">
-        <v>27.688213934076799</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+        <v>27.6882139340768</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
-        <v>1.3308956623077399</v>
+        <v>1.33089566230774</v>
       </c>
       <c r="C18">
         <v>-2.10699725119707</v>
@@ -1308,16 +1283,16 @@
         <v>11.8881592273253</v>
       </c>
       <c r="F18">
-        <v>1.8194514762052201</v>
+        <v>1.81945147620522</v>
       </c>
       <c r="G18">
-        <v>57976.628204291002</v>
+        <v>57976.628204291</v>
       </c>
       <c r="H18">
-        <v>22.415921839149199</v>
+        <v>22.4159218391492</v>
       </c>
       <c r="I18">
-        <v>18.540821220497001</v>
+        <v>18.540821220497</v>
       </c>
       <c r="J18">
         <v>14.5644385592212</v>
@@ -1326,22 +1301,22 @@
         <v>1.26158320570536</v>
       </c>
       <c r="L18">
-        <v>8.2003260222903496</v>
+        <v>8.20032602229035</v>
       </c>
       <c r="M18">
-        <v>-3.8302022455514702</v>
+        <v>-3.83020224555147</v>
       </c>
       <c r="N18">
         <v>0.385635316371918</v>
       </c>
       <c r="O18">
-        <v>10.854514987652401</v>
+        <v>10.8545149876524</v>
       </c>
       <c r="P18">
-        <v>26.452597786546502</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+        <v>26.4525977865465</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
@@ -1349,40 +1324,40 @@
         <v>1.34053254127502</v>
       </c>
       <c r="C19">
-        <v>-1.8744242712994299</v>
+        <v>-1.87442427129943</v>
       </c>
       <c r="D19">
         <v>106.4</v>
       </c>
       <c r="E19">
-        <v>12.177481026765999</v>
+        <v>12.177481026766</v>
       </c>
       <c r="F19">
         <v>2.45762230175086</v>
       </c>
       <c r="G19">
-        <v>60047.719072830703</v>
+        <v>60047.7190728307</v>
       </c>
       <c r="H19">
-        <v>22.140699655753401</v>
+        <v>22.1406996557534</v>
       </c>
       <c r="I19">
         <v>19.2095273622379</v>
       </c>
       <c r="J19">
-        <v>14.947857195521401</v>
+        <v>14.9478571955214</v>
       </c>
       <c r="K19">
-        <v>2.1301100036596101</v>
+        <v>2.13011000365961</v>
       </c>
       <c r="L19">
-        <v>8.4988413628066102</v>
+        <v>8.49884136280661</v>
       </c>
       <c r="M19">
-        <v>-2.9441831375341598</v>
+        <v>-2.94418313753416</v>
       </c>
       <c r="N19">
-        <v>0.26213830709457397</v>
+        <v>0.262138307094574</v>
       </c>
       <c r="O19">
         <v>11.5038867327939</v>
@@ -1391,7 +1366,7 @@
         <v>27.1253382222874</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
@@ -1399,7 +1374,7 @@
         <v>1.2927473783493</v>
       </c>
       <c r="C20">
-        <v>-2.1251841307604802</v>
+        <v>-2.12518413076048</v>
       </c>
       <c r="D20">
         <v>107.6</v>
@@ -1408,98 +1383,98 @@
         <v>12.2871107596266</v>
       </c>
       <c r="F20">
-        <v>2.9665050691659598</v>
+        <v>2.96650506916596</v>
       </c>
       <c r="G20">
-        <v>62875.666138272798</v>
+        <v>62875.6661382728</v>
       </c>
       <c r="H20">
         <v>22.1694791125473</v>
       </c>
       <c r="I20">
-        <v>17.479358571406699</v>
+        <v>17.4793585714067</v>
       </c>
       <c r="J20">
-        <v>15.158248370635199</v>
+        <v>15.1582483706352</v>
       </c>
       <c r="K20">
         <v>2.44258329692817</v>
       </c>
       <c r="L20">
-        <v>9.6709206056109007</v>
+        <v>9.670920605610901</v>
       </c>
       <c r="M20">
-        <v>-4.7789985494165599</v>
+        <v>-4.77899854941656</v>
       </c>
       <c r="N20">
-        <v>0.38623908162116999</v>
+        <v>0.38623908162117</v>
       </c>
       <c r="O20">
-        <v>9.9295389406422707</v>
+        <v>9.929538940642271</v>
       </c>
       <c r="P20">
-        <v>27.445359130261799</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+        <v>27.4453591302618</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
-        <v>1.1803570985794101</v>
+        <v>1.18035709857941</v>
       </c>
       <c r="C21">
-        <v>-2.0518215846234198</v>
+        <v>-2.05182158462342</v>
       </c>
       <c r="D21">
         <v>108.8</v>
       </c>
       <c r="E21">
-        <v>11.789197409728599</v>
+        <v>11.7891974097286</v>
       </c>
       <c r="F21">
         <v>2.58382533018889</v>
       </c>
       <c r="G21">
-        <v>65227.956591103801</v>
+        <v>65227.9565911038</v>
       </c>
       <c r="H21">
-        <v>22.514337755713999</v>
+        <v>22.514337755714</v>
       </c>
       <c r="I21">
-        <v>17.291377959368798</v>
+        <v>17.2913779593688</v>
       </c>
       <c r="J21">
-        <v>14.469283214814199</v>
+        <v>14.4692832148142</v>
       </c>
       <c r="K21">
-        <v>1.8122100752602099</v>
+        <v>1.81221007526021</v>
       </c>
       <c r="L21">
-        <v>9.8284506571006496</v>
+        <v>9.82845065710065</v>
       </c>
       <c r="M21">
-        <v>-5.3587867436472303</v>
+        <v>-5.35878674364723</v>
       </c>
       <c r="N21">
         <v>0.118298575282097</v>
       </c>
       <c r="O21">
-        <v>9.8847895973172104</v>
+        <v>9.88478959731721</v>
       </c>
       <c r="P21">
-        <v>26.258480624542798</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+        <v>26.2584806245428</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
-        <v>1.0378319025039699</v>
+        <v>1.03783190250397</v>
       </c>
       <c r="C22">
-        <v>-2.7793438310807201</v>
+        <v>-2.77934383108072</v>
       </c>
       <c r="D22">
         <v>132.5</v>
@@ -1508,16 +1483,16 @@
         <v>10.0736556273372</v>
       </c>
       <c r="F22">
-        <v>-2.1630291386651201</v>
+        <v>-2.16302913866512</v>
       </c>
       <c r="G22">
-        <v>64401.507435421197</v>
+        <v>64401.5074354212</v>
       </c>
       <c r="H22">
         <v>31.8281473281133</v>
       </c>
       <c r="I22">
-        <v>17.708696290479001</v>
+        <v>17.708696290479</v>
       </c>
       <c r="J22">
         <v>13.0061222420701</v>
@@ -1532,21 +1507,21 @@
         <v>-14.3606964562551</v>
       </c>
       <c r="N22">
-        <v>-2.7899732813239101E-2</v>
+        <v>-0.0278997328132391</v>
       </c>
       <c r="O22">
-        <v>10.153422023540699</v>
+        <v>10.1534220235407</v>
       </c>
       <c r="P22">
-        <v>23.079777869407302</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+        <v>23.0797778694073</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
-        <v>1.0192775726318399</v>
+        <v>1.01927757263184</v>
       </c>
       <c r="C23">
         <v>-3.62580887575196</v>
@@ -1558,63 +1533,63 @@
         <v>10.7909781995156</v>
       </c>
       <c r="F23">
-        <v>6.0550529330455598</v>
+        <v>6.05505293304556</v>
       </c>
       <c r="G23">
-        <v>71307.401727721794</v>
+        <v>71307.40172772179</v>
       </c>
       <c r="H23">
-        <v>31.303476082327201</v>
+        <v>31.3034760823272</v>
       </c>
       <c r="I23">
-        <v>18.808352424801999</v>
+        <v>18.808352424802</v>
       </c>
       <c r="J23">
         <v>14.422677831261</v>
       </c>
       <c r="K23">
-        <v>4.6978588636374203</v>
+        <v>4.69785886363742</v>
       </c>
       <c r="L23">
-        <v>6.8484778902207797</v>
+        <v>6.84847789022078</v>
       </c>
       <c r="M23">
         <v>-12.6578436513971</v>
       </c>
       <c r="N23">
-        <v>-1.44246527925134E-2</v>
+        <v>-0.0144246527925134</v>
       </c>
       <c r="O23">
         <v>11.394678497951</v>
       </c>
       <c r="P23">
-        <v>25.213656030776502</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+        <v>25.2136560307765</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>1.1041446924209599</v>
+        <v>1.10414469242096</v>
       </c>
       <c r="C24">
-        <v>-3.8187645098551402</v>
+        <v>-3.81876450985514</v>
       </c>
       <c r="D24">
         <v>119.1</v>
       </c>
       <c r="E24">
-        <v>11.602227917037199</v>
+        <v>11.6022279170372</v>
       </c>
       <c r="F24">
-        <v>2.5123753198331999</v>
+        <v>2.5123753198332</v>
       </c>
       <c r="G24">
-        <v>77860.911290884804</v>
+        <v>77860.9112908848</v>
       </c>
       <c r="H24">
-        <v>24.658458048025999</v>
+        <v>24.658458048026</v>
       </c>
       <c r="I24">
         <v>19.9277753017248</v>
@@ -1623,30 +1598,30 @@
         <v>15.2894619130397</v>
       </c>
       <c r="K24">
-        <v>8.0027998205212096</v>
+        <v>8.00279982052121</v>
       </c>
       <c r="L24">
-        <v>10.835538212453899</v>
+        <v>10.8355382124539</v>
       </c>
       <c r="M24">
-        <v>-4.4189773072854202</v>
+        <v>-4.41897730728542</v>
       </c>
       <c r="N24">
-        <v>8.7006865069270099E-3</v>
+        <v>0.00870068650692701</v>
       </c>
       <c r="O24">
         <v>12.5989036829582</v>
       </c>
       <c r="P24">
-        <v>26.891689830076999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+        <v>26.891689830077</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>1.1234326362609901</v>
+        <v>1.12343263626099</v>
       </c>
       <c r="C25">
         <v>-3.34773904953152</v>
@@ -1655,47 +1630,46 @@
         <v>119.8</v>
       </c>
       <c r="E25">
-        <v>11.011511285660101</v>
+        <v>11.0115112856601</v>
       </c>
       <c r="F25">
         <v>2.88755600905984</v>
       </c>
       <c r="G25">
-        <v>82304.620427286602</v>
+        <v>82304.6204272866</v>
       </c>
       <c r="H25">
-        <v>24.513376623952901</v>
+        <v>24.5133766239529</v>
       </c>
       <c r="I25">
-        <v>17.592195784025598</v>
+        <v>17.5921957840256</v>
       </c>
       <c r="J25">
         <v>13.8878518583345</v>
       </c>
       <c r="K25">
-        <v>4.1163383837448801</v>
+        <v>4.11633838374488</v>
       </c>
       <c r="L25">
-        <v>12.908112213977599</v>
+        <v>12.9081122139776</v>
       </c>
       <c r="M25">
-        <v>-7.1419107642593103</v>
+        <v>-7.14191076425931</v>
       </c>
       <c r="N25">
-        <v>2.9424749314785E-2</v>
+        <v>0.029424749314785</v>
       </c>
       <c r="O25">
-        <v>10.645912772288799</v>
+        <v>10.6459127722888</v>
       </c>
       <c r="P25">
-        <v>24.899363143994599</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+        <v>24.8993631439946</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26" s="2"/>
       <c r="C26">
         <v>-4.06132762535682</v>
       </c>
@@ -1703,30 +1677,25 @@
         <v>122.3</v>
       </c>
       <c r="E26">
-        <v>10.896875061033301</v>
+        <v>10.8968750610333</v>
       </c>
       <c r="F26">
-        <v>2.7961903562139301</v>
+        <v>2.79619035621393</v>
       </c>
       <c r="G26">
-        <v>85809.900384635606</v>
-      </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+        <v>85809.90038463561</v>
+      </c>
       <c r="J26">
         <v>13.9911166360401</v>
       </c>
       <c r="K26">
-        <v>2.9495252048520699</v>
-      </c>
-      <c r="L26" s="2"/>
+        <v>2.94952520485207</v>
+      </c>
       <c r="M26">
         <v>-8</v>
       </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
       <c r="P26">
-        <v>24.887991697073399</v>
+        <v>24.8879916970734</v>
       </c>
     </row>
   </sheetData>
